--- a/demo/剧本表_ch01.xlsx
+++ b/demo/剧本表_ch01.xlsx
@@ -16,7 +16,10 @@
     <sheet name="Candidates_语音" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="词表" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="使用说明" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="舞台快照" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="资源图库" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="舞台快照" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="演出时间轴" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="列说明" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="CAND_CHARACTER">OFFSET('Candidates_角色'!$A$3,0,0,MAX(COUNTA('Candidates_角色'!$A$3:$A$5000),1),1)</definedName>
@@ -25,6 +28,8 @@
     <definedName name="CAND_MUSIC">OFFSET('Candidates_音乐'!$A$3,0,0,MAX(COUNTA('Candidates_音乐'!$A$3:$A$5000),1),1)</definedName>
     <definedName name="CAND_SOUND">OFFSET('Candidates_音效'!$A$3,0,0,MAX(COUNTA('Candidates_音效'!$A$3:$A$5000),1),1)</definedName>
     <definedName name="CAND_VOICE">OFFSET('Candidates_语音'!$A$3,0,0,MAX(COUNTA('Candidates_语音'!$A$3:$A$5000),1),1)</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Beats'!$A$1:$T$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'演出时间轴'!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +49,23 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+    </font>
+    <font>
+      <color rgb="00909090"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F4F00"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +75,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -70,12 +100,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -445,29 +499,29 @@
   <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
     <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-    <col width="32" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>行号</t>
@@ -569,7 +623,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
           <t>ch01.0001</t>
@@ -629,11 +683,11 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2b93371142</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>6ccbcf2f09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>ch01.0002</t>
@@ -685,11 +739,11 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>160225a63e</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>af4a87ffd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>ch01.0003</t>
@@ -749,11 +803,11 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>253cb8d2f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>5bdf06dc58</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>ch01.0004</t>
@@ -793,11 +847,12 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>9a8e844fbb</t>
+          <t>6bc464952b</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T5"/>
   <dataValidations count="10">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="说话人" prompt="从角色表选（也可直接写角色变量名）" type="list">
       <formula1>CAND_CHARACTER</formula1>
@@ -840,254 +895,1495 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>↓ 资源图库：由资源表 + 脚本自动生成，**只读**（改这里没用，请改资源表）。「引用次数」= 脚本里用到几次，0 表示还没人用。界面/系统资源统一放在最后一段，策划通常不用管。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>▌背景　（2 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>bg_classroom</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>背景 · tag=bg · 属性=bg_classroom · game/images/bg/bg_classroom.png</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>game/images/bg/bg_classroom.png</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>bg_rooftop</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>背景 · tag=bg · 属性=bg_rooftop · game/images/bg/bg_rooftop.png</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>game/images/bg/bg_rooftop.png</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>▌其他图　（4 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=happy · game/images/eileen/happy.png</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>game/images/eileen/happy.png</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>happy_blush</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=happy_blush · game/images/eileen/happy_blush.png</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>game/images/eileen/happy_blush.png</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>sad</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>其他 · tag=eileen · 属性=sad · game/images/eileen/sad.png</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>game/images/eileen/sad.png</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>smile</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>其他 · tag=mary · 属性=smile · game/images/mary/smile.png</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>game/images/mary/smile.png</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>▌音乐　（2 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>bgm_night</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>game/music/night.ogg · 循环 · 音量 1</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>game/music/night.ogg</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>bgm_rain</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>game/music/rain.ogg · 循环 · 音量 1</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>game/music/rain.ogg</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>▌音效　（2 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>sfx_click</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>game/sounds/click.ogg</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>game/sounds/click.ogg</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>sfx_door</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>game/sounds/door.ogg</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>game/sounds/door.ogg</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>▌语音　（2 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>v_eileen_01</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_01.ogg</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_01.ogg</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>v_eileen_02</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_02.ogg</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>game/voice/v_eileen_02.ogg</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>▌自定义变换　（3 项）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>ID（可直接写进表格）</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>真实文件</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>引用次数</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>贴图预览</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>fade_in_soft</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>柔和淡入，用于回忆切入 · custom · ATL 2 行</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr"/>
+      <c r="D27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>leftish</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>靠左站，双人对话时主角在左 · custom · ATL 2 行</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr"/>
+      <c r="D28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>shake_hard</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>剧烈抖动，挨打/惊吓演出用 · 参数 t=0.05, n=6 · custom · ATL 5 行</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LineId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>章节</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>说话人</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>台词</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>本拍变化</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>背景</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>立绘（谁·在哪）</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CG·图层</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>音乐</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>音效</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>早上好，昨晚睡得好吗？</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>+ eileen happy @ leftish（登场）
+♪ 音乐 → night fadein 1.0
+背景 → bg classroom</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>bg classroom</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>eileen happy@leftish</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr"/>
+      <c r="L2" s="7" t="inlineStr"/>
+      <c r="M2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>还行，就是雨下了一整晚。</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>♫ 音效 door
+🎙 语音 v_eileen_01</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>bg classroom</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>eileen happy@leftish</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr"/>
+      <c r="J3" s="10" t="inlineStr">
+        <is>
+          <t>night</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>door</t>
+        </is>
+      </c>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>v_eileen_01</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>音效 door</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>别想了，今天我们还有正事。</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>− eileen（退场）
++ eileen sad @ leftish（登场）
++ mary smile @ right（登场）
+♪ 音乐 → rain fadeout 2.0</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>bg classroom</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
+        <is>
+          <t>eileen sad@leftish; mary smile@right</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>rain</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr">
+        <is>
+          <t>原始语句</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>♪ 停止音乐</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>bg classroom</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>eileen sad@leftish; mary smile@right</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="7" t="inlineStr"/>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LineId</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Seq</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>章节</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>说话人</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>台词</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>本拍变化</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0001</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>e</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>早上好，昨晚睡得好吗？</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>+ eileen happy @ leftish（登场）
+♪ 音乐 → night fadein 1.0
+背景 → bg classroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0002</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>还行，就是雨下了一整晚。</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>♫ 音效 door
+🎙 语音 v_eileen_01</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0003</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>别想了，今天我们还有正事。</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>− eileen（退场）
++ eileen sad @ leftish（登场）
++ mary smile @ right（登场）
+♪ 音乐 → rain fadeout 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ch01.0004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>ch01</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr"/>
+      <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>♪ 停止音乐</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>LineId</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Seq</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>说话人</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>台词</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
-        <is>
-          <t>背景</t>
-        </is>
-      </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>立绘（谁·在哪）</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>音乐</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>音效</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>语音</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>备注</t>
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>列</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>属于</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>给谁看</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>怎么填</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ch01.0001</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
+          <t>行号 LineId</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>程序区</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ch01</t>
+          <t>协作/追溯</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>e</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>早上好，昨晚睡得好吗？</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>bg classroom</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>eileen happy@leftish</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>自动生成，别改</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ch01.0002</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
+          <t>序号 Seq</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>程序区</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ch01</t>
+          <t>排序</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>还行，就是雨下了一整晚。</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>bg classroom</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>eileen happy@leftish</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>night</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>door</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>v_eileen_01</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>音效 door</t>
+          <t>自动生成</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ch01.0003</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>3</v>
+          <t>章节 Label</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ch01</t>
+          <t>策划</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>别想了，今天我们还有正事。</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>bg classroom</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>eileen sad@leftish; mary smile@right</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>rain</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>原始语句</t>
+          <t>这一行属于哪个 label</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ch01.0004</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>4</v>
+          <t>类型 Kind</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ch01</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>bg classroom</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>eileen sad@leftish; mary smile@right</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>下拉：说话/旁白/菜单/菜单选项/延续</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>说话人 Speaker</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>下拉选角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>注释 Comment</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>给自己/同事看的备注，会写进脚本注释</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>台词 Text</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>这一句台词</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>背景 Scene</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>下拉选背景；`图@变换` 可带背景变换</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>立绘 Show</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>下拉选图；`图@位置` 指定站位</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>位置 At</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>没用 @ 指定站位的立绘统一用这列</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>转场 With</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>下拉选转场</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>退场 Hide</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>下拉选图；`图@转场` 可带退场转场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>音乐 BGM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>下拉选音乐；也可选「（停止音乐）」</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>音乐参数 BGMParams</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>如 `fadein 1.0`</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>音效 SFX</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>下拉选音效；也可选「（停止音效）」</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>音效参数 SFXParams</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>如 `volume 0.5`</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>语音 Voice</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>编辑区</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>策划</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>下拉选语音</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>舞台（高级）Stage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>高级区</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>策划（进阶）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>结构化列表达不了的指令；人话或原生写法都行</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>代码 CodeBlock</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>程序区</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>程序</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>原样抄进脚本的逃生舱，不解析不校验</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>内容指纹 ContentHash</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>程序区</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>协作</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>自动重算，别改</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/demo/剧本表_ch01.xlsx
+++ b/demo/剧本表_ch01.xlsx
@@ -28,7 +28,7 @@
     <definedName name="CAND_MUSIC">OFFSET('Candidates_音乐'!$A$3,0,0,MAX(COUNTA('Candidates_音乐'!$A$3:$A$5000),1),1)</definedName>
     <definedName name="CAND_SOUND">OFFSET('Candidates_音效'!$A$3,0,0,MAX(COUNTA('Candidates_音效'!$A$3:$A$5000),1),1)</definedName>
     <definedName name="CAND_VOICE">OFFSET('Candidates_语音'!$A$3,0,0,MAX(COUNTA('Candidates_语音'!$A$3:$A$5000),1),1)</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Beats'!$A$1:$T$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Beats'!$A$1:$V$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'演出时间轴'!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -519,6 +519,8 @@
     <col width="36" customWidth="1" min="18" max="18"/>
     <col width="30" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
+    <col hidden="1" width="16" customWidth="1" min="21" max="21"/>
+    <col hidden="1" width="16" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -622,6 +624,16 @@
           <t>内容指纹</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>舞台顺序（内部）</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>操作顺序（内部）</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="45" customHeight="1">
       <c r="A2" t="inlineStr">
@@ -662,7 +674,11 @@
           <t>bg classroom</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>eileen happy@leftish</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -675,15 +691,21 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>[显示] 爱莲 开心 at leftish</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
           <t>6ccbcf2f09</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>scene,show</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>stage,audio</t>
         </is>
       </c>
     </row>
@@ -742,6 +764,12 @@
           <t>af4a87ffd5</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>voice,audio</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -774,7 +802,11 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>eileen sad@leftish; mary smile@right</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
@@ -791,11 +823,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>[显示] 爱莲 难过 at leftish; [显示] 玛丽 笑 右</t>
-        </is>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>with dissolve</t>
@@ -804,6 +832,16 @@
       <c r="T4" t="inlineStr">
         <is>
           <t>5bdf06dc58</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>hide,show</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>stage,audio</t>
         </is>
       </c>
     </row>
@@ -850,9 +888,15 @@
           <t>6bc464952b</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>audio</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T5"/>
+  <autoFilter ref="A1:V5"/>
   <dataValidations count="10">
     <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="说话人" prompt="从角色表选（也可直接写角色变量名）" type="list">
       <formula1>CAND_CHARACTER</formula1>
